--- a/tools/sheets/item.xlsx
+++ b/tools/sheets/item.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,9 @@
       <family val="3"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,9 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -476,6 +480,21 @@
           <t>dice_bonus</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>equip_slot</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>bag_slots</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -506,6 +525,9 @@
       <c r="F2" t="n">
         <v>5</v>
       </c>
+      <c r="H2" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,6 +558,14 @@
           <t>strength+1</t>
         </is>
       </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -561,6 +591,9 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -591,6 +624,9 @@
       <c r="F5" t="n">
         <v>3</v>
       </c>
+      <c r="H5" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -621,6 +657,9 @@
       <c r="F6" t="n">
         <v>5</v>
       </c>
+      <c r="H6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -651,6 +690,9 @@
       <c r="F7" t="n">
         <v>5</v>
       </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -675,6 +717,45 @@
       </c>
       <c r="F8" t="n">
         <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>small_bag</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>작은 가방(테스트)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>equip</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>장착하면 소지품 칸 +4</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>bag</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -688,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -886,6 +967,32 @@
         <v>5</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>l7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>spot_charm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>small_bag</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -897,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -938,6 +1045,13 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Items.weight: 무게(개당). equip_slot: 장착 칸(player.xlsx EquipSlots 의 slot_id). bag_slots: 장착하면 늘어나는 소지품 칸 수 (가방)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tools/sheets/item.xlsx
+++ b/tools/sheets/item.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>weapon</t>
+          <t>hand</t>
         </is>
       </c>
     </row>
@@ -1017,6 +1017,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1048,7 +1049,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Items.weight: 무게(개당). equip_slot: 장착 칸(player.xlsx EquipSlots 의 slot_id). bag_slots: 장착하면 늘어나는 소지품 칸 수 (가방)</t>
+          <t>Items.weight: 무게(개당). equip_slot: 장착 종류 (player.xlsx EquipSlots 의 kind — bag, head, hand, body, leg). 비워도 손에는 들 수 있음. bag_slots: 장착하면 늘어나는 소지품 칸 수 (가방)</t>
         </is>
       </c>
     </row>

--- a/tools/sheets/item.xlsx
+++ b/tools/sheets/item.xlsx
@@ -63,10 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.25" customWidth="1" min="1" max="1"/>
@@ -495,6 +496,11 @@
           <t>bag_slots</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -756,6 +762,44 @@
       </c>
       <c r="J9" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>flashlight</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>손전등(테스트)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>손에 들면 앞을 비춘다</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>flashlight</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1061,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
